--- a/ruby/spec/test_data/テーブル.xlsx
+++ b/ruby/spec/test_data/テーブル.xlsx
@@ -234,7 +234,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="テーブル1" displayName="テーブル1" ref="A1:C3" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="プロパティ名マッピング" displayName="プロパティ名マッピング" ref="A1:C3" totalsRowShown="0">
   <autoFilter ref="A1:C3"/>
   <tableColumns count="3">
     <tableColumn id="1" name="float"/>
@@ -246,7 +246,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="テーブル2" displayName="テーブル2" ref="B6:E9" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="型付き行マッピング" displayName="型付き行マッピング" ref="B6:E9" totalsRowShown="0">
   <autoFilter ref="B6:E9"/>
   <tableColumns count="4">
     <tableColumn id="1" name="数値"/>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="テーブル28" displayName="テーブル28" ref="G4:J7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="別テーブル列検証" displayName="別テーブル列検証" ref="G4:J7" totalsRowShown="0">
   <autoFilter ref="G4:J7"/>
   <tableColumns count="4">
     <tableColumn id="1" name="数値"/>
@@ -272,7 +272,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="テーブル3" displayName="テーブル3" ref="A1:B5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="空行マッピング" displayName="空行マッピング" ref="A1:B5" totalsRowShown="0">
   <autoFilter ref="A1:B5"/>
   <tableColumns count="2">
     <tableColumn id="1" name="列1"/>
@@ -283,7 +283,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="テーブル4" displayName="テーブル4" ref="A9:B14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="左下空テーブル" displayName="左下空テーブル" ref="A9:B14" totalsRowShown="0">
   <autoFilter ref="A9:B14"/>
   <tableColumns count="2">
     <tableColumn id="1" name="列1"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="テーブル5" displayName="テーブル5" ref="D6:E13" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="中央空テーブル" displayName="中央空テーブル" ref="D6:E13" totalsRowShown="0">
   <autoFilter ref="D6:E13"/>
   <tableColumns count="2">
     <tableColumn id="1" name="列1"/>
@@ -305,7 +305,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="テーブル8" displayName="テーブル8" ref="G11:H19" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="右下空テーブル" displayName="右下空テーブル" ref="G11:H19" totalsRowShown="0">
   <autoFilter ref="G11:H19"/>
   <tableColumns count="2">
     <tableColumn id="1" name="列1"/>
@@ -316,7 +316,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="テーブル6" displayName="テーブル6" ref="A1:C12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="別シート行列挙" displayName="別シート行列挙" ref="A1:C12" totalsRowShown="0">
   <autoFilter ref="A1:C12"/>
   <tableColumns count="3">
     <tableColumn id="1" name="int"/>
